--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 2 3 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA90CBE-79F0-412E-AA78-78C34AA33B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8798D671-E798-4ABF-823C-27E61BC2478E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="176">
   <si>
     <t>CPF</t>
   </si>
@@ -163,6 +163,12 @@
     <t>SUSANY ROCHA ALBINO</t>
   </si>
   <si>
+    <t>912.132.741-68</t>
+  </si>
+  <si>
+    <t>SIMONE MACHADO GOMES</t>
+  </si>
+  <si>
     <t>942.860.191-87</t>
   </si>
   <si>
@@ -364,6 +370,9 @@
     <t>SENHA</t>
   </si>
   <si>
+    <t>MARCIA PONCE</t>
+  </si>
+  <si>
     <t>CENTRO DE ENSINO MEDIO ARY RIBEIRO VALADAO FILHO</t>
   </si>
   <si>
@@ -532,14 +541,23 @@
     <t>626.250.041-34</t>
   </si>
   <si>
+    <t>832.866.401-15</t>
+  </si>
+  <si>
     <t>ESCOLA ESTADUAL PROFESSORA DIVA GOMES DA SILVEIRA COSTA</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>alexandre_royal@seduc.to.gov.br</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -548,6 +566,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -567,14 +591,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -887,15 +914,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -903,13 +931,16 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="E1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -920,7 +951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -931,18 +962,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -953,7 +984,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -964,7 +995,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -975,7 +1006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -986,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -997,7 +1028,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1008,7 +1039,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1019,7 +1050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1030,7 +1061,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1041,7 +1072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1052,7 +1083,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1063,7 +1094,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1074,7 +1105,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -1085,7 +1116,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1096,7 +1127,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1107,7 +1138,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -1118,7 +1149,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1129,7 +1160,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -1139,8 +1170,11 @@
       <c r="D22" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -1151,7 +1185,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -1162,7 +1196,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -1173,7 +1207,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -1184,7 +1218,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -1195,7 +1229,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -1206,7 +1240,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -1217,7 +1251,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -1228,7 +1262,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -1239,7 +1273,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -1362,46 +1396,46 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D44" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="D46" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1417,431 +1451,431 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D48" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="D49" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="B50" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D50" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D52" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D53" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="D54" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="D55" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="D56" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D57" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D58" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D59" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="B60" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="D60" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="D61" t="s">
-        <v>2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D63" t="s">
-        <v>72</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D64" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="D65" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="D66" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="B67" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="D67" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D69" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D71" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="D72" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="D74" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B75" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B76" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="D78" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="D79" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D80" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="D81" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D82" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D83" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D84" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="B85" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="D85" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B86" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D86" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -1857,112 +1891,112 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B88" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D88" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="D89" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="B90" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="D90" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="B91" t="s">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="D91" t="s">
-        <v>108</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B92" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D92" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="B93" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>113</v>
       </c>
-      <c r="C94">
+      <c r="B94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>59</v>
+      </c>
+      <c r="B95" t="s">
+        <v>58</v>
+      </c>
+      <c r="D95" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>115</v>
+      </c>
+      <c r="B96" t="s">
+        <v>172</v>
+      </c>
+      <c r="D96" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>116</v>
+      </c>
+      <c r="C97">
         <v>17021502</v>
       </c>
-      <c r="D94">
+      <c r="D97">
         <v>17021502</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C95">
-        <v>17021685</v>
-      </c>
-      <c r="D95">
-        <v>17021685</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C96">
-        <v>17021553</v>
-      </c>
-      <c r="D96">
-        <v>17021553</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C97">
-        <v>17052351</v>
-      </c>
-      <c r="D97">
-        <v>17052351</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -1970,10 +2004,10 @@
         <v>117</v>
       </c>
       <c r="C98">
-        <v>17021243</v>
+        <v>17021685</v>
       </c>
       <c r="D98">
-        <v>17021243</v>
+        <v>17021685</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -1981,10 +2015,10 @@
         <v>118</v>
       </c>
       <c r="C99">
-        <v>17023181</v>
+        <v>17021553</v>
       </c>
       <c r="D99">
-        <v>17023181</v>
+        <v>17021553</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -1992,10 +2026,10 @@
         <v>119</v>
       </c>
       <c r="C100">
-        <v>17048826</v>
+        <v>17052351</v>
       </c>
       <c r="D100">
-        <v>17048826</v>
+        <v>17052351</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -2003,10 +2037,10 @@
         <v>120</v>
       </c>
       <c r="C101">
-        <v>17020336</v>
+        <v>17021243</v>
       </c>
       <c r="D101">
-        <v>17020336</v>
+        <v>17021243</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -2014,10 +2048,10 @@
         <v>121</v>
       </c>
       <c r="C102">
-        <v>17018382</v>
+        <v>17023181</v>
       </c>
       <c r="D102">
-        <v>17018382</v>
+        <v>17023181</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -2025,10 +2059,10 @@
         <v>122</v>
       </c>
       <c r="C103">
-        <v>17021251</v>
+        <v>17048826</v>
       </c>
       <c r="D103">
-        <v>17021251</v>
+        <v>17048826</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -2036,10 +2070,10 @@
         <v>123</v>
       </c>
       <c r="C104">
-        <v>17020590</v>
+        <v>17020336</v>
       </c>
       <c r="D104">
-        <v>17020590</v>
+        <v>17020336</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -2047,10 +2081,10 @@
         <v>124</v>
       </c>
       <c r="C105">
-        <v>17052963</v>
+        <v>17018382</v>
       </c>
       <c r="D105">
-        <v>17052963</v>
+        <v>17018382</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -2058,10 +2092,10 @@
         <v>125</v>
       </c>
       <c r="C106">
-        <v>17022819</v>
+        <v>17021251</v>
       </c>
       <c r="D106">
-        <v>17022819</v>
+        <v>17021251</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -2069,10 +2103,10 @@
         <v>126</v>
       </c>
       <c r="C107">
-        <v>17017912</v>
+        <v>17020590</v>
       </c>
       <c r="D107">
-        <v>17017912</v>
+        <v>17020590</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -2080,10 +2114,10 @@
         <v>127</v>
       </c>
       <c r="C108">
-        <v>17055857</v>
+        <v>17052963</v>
       </c>
       <c r="D108">
-        <v>17055857</v>
+        <v>17052963</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -2091,10 +2125,10 @@
         <v>128</v>
       </c>
       <c r="C109">
-        <v>17021561</v>
+        <v>17022819</v>
       </c>
       <c r="D109">
-        <v>17021561</v>
+        <v>17022819</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -2102,10 +2136,10 @@
         <v>129</v>
       </c>
       <c r="C110">
-        <v>17017165</v>
+        <v>17017912</v>
       </c>
       <c r="D110">
-        <v>17017165</v>
+        <v>17017912</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -2113,54 +2147,54 @@
         <v>130</v>
       </c>
       <c r="C111">
-        <v>17020140</v>
+        <v>17055857</v>
       </c>
       <c r="D111">
-        <v>17020140</v>
+        <v>17055857</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="C112">
-        <v>17023319</v>
+        <v>17021561</v>
       </c>
       <c r="D112">
-        <v>17023319</v>
+        <v>17021561</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C113">
-        <v>17040051</v>
+        <v>17017165</v>
       </c>
       <c r="D113">
-        <v>17040051</v>
+        <v>17017165</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C114">
-        <v>17021596</v>
+        <v>17020140</v>
       </c>
       <c r="D114">
-        <v>17021596</v>
+        <v>17020140</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="C115">
-        <v>17022320</v>
+        <v>17023319</v>
       </c>
       <c r="D115">
-        <v>17022320</v>
+        <v>17023319</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -2168,10 +2202,10 @@
         <v>134</v>
       </c>
       <c r="C116">
-        <v>17036917</v>
+        <v>17040051</v>
       </c>
       <c r="D116">
-        <v>17036917</v>
+        <v>17040051</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -2179,10 +2213,10 @@
         <v>135</v>
       </c>
       <c r="C117">
-        <v>17021146</v>
+        <v>17021596</v>
       </c>
       <c r="D117">
-        <v>17021146</v>
+        <v>17021596</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -2190,10 +2224,10 @@
         <v>136</v>
       </c>
       <c r="C118">
-        <v>17018390</v>
+        <v>17022320</v>
       </c>
       <c r="D118">
-        <v>17018390</v>
+        <v>17022320</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -2201,10 +2235,10 @@
         <v>137</v>
       </c>
       <c r="C119">
-        <v>17020581</v>
+        <v>17036917</v>
       </c>
       <c r="D119">
-        <v>17020581</v>
+        <v>17036917</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -2212,10 +2246,10 @@
         <v>138</v>
       </c>
       <c r="C120">
-        <v>17022312</v>
+        <v>17021146</v>
       </c>
       <c r="D120">
-        <v>17022312</v>
+        <v>17021146</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -2223,10 +2257,10 @@
         <v>139</v>
       </c>
       <c r="C121">
-        <v>17021774</v>
+        <v>17018390</v>
       </c>
       <c r="D121">
-        <v>17021774</v>
+        <v>17018390</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -2234,10 +2268,10 @@
         <v>140</v>
       </c>
       <c r="C122">
-        <v>17022339</v>
+        <v>17020581</v>
       </c>
       <c r="D122">
-        <v>17022339</v>
+        <v>17020581</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -2245,10 +2279,10 @@
         <v>141</v>
       </c>
       <c r="C123">
-        <v>17040035</v>
+        <v>17022312</v>
       </c>
       <c r="D123">
-        <v>17040035</v>
+        <v>17022312</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -2256,10 +2290,10 @@
         <v>142</v>
       </c>
       <c r="C124">
-        <v>17022860</v>
+        <v>17021774</v>
       </c>
       <c r="D124">
-        <v>17022860</v>
+        <v>17021774</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -2267,10 +2301,10 @@
         <v>143</v>
       </c>
       <c r="C125">
-        <v>17020611</v>
+        <v>17022339</v>
       </c>
       <c r="D125">
-        <v>17020611</v>
+        <v>17022339</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -2278,10 +2312,10 @@
         <v>144</v>
       </c>
       <c r="C126">
-        <v>17021588</v>
+        <v>17040035</v>
       </c>
       <c r="D126">
-        <v>17021588</v>
+        <v>17040035</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -2289,10 +2323,10 @@
         <v>145</v>
       </c>
       <c r="C127">
-        <v>17038359</v>
+        <v>17022860</v>
       </c>
       <c r="D127">
-        <v>17038359</v>
+        <v>17022860</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -2300,10 +2334,10 @@
         <v>146</v>
       </c>
       <c r="C128">
-        <v>17018404</v>
+        <v>17020611</v>
       </c>
       <c r="D128">
-        <v>17018404</v>
+        <v>17020611</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -2311,10 +2345,10 @@
         <v>147</v>
       </c>
       <c r="C129">
-        <v>17021731</v>
+        <v>17021588</v>
       </c>
       <c r="D129">
-        <v>17021731</v>
+        <v>17021588</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -2322,54 +2356,54 @@
         <v>148</v>
       </c>
       <c r="C130">
-        <v>17020360</v>
+        <v>17038359</v>
       </c>
       <c r="D130">
-        <v>17020360</v>
+        <v>17038359</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="C131">
-        <v>17040841</v>
+        <v>17018404</v>
       </c>
       <c r="D131">
-        <v>17040841</v>
+        <v>17018404</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C132">
-        <v>17020158</v>
+        <v>17021731</v>
       </c>
       <c r="D132">
-        <v>17020158</v>
+        <v>17021731</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C133">
-        <v>17053315</v>
+        <v>17020360</v>
       </c>
       <c r="D133">
-        <v>17053315</v>
+        <v>17020360</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C134">
-        <v>17021600</v>
+        <v>17040841</v>
       </c>
       <c r="D134">
-        <v>17021600</v>
+        <v>17040841</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
@@ -2377,10 +2411,10 @@
         <v>152</v>
       </c>
       <c r="C135">
-        <v>17017203</v>
+        <v>17020158</v>
       </c>
       <c r="D135">
-        <v>17017203</v>
+        <v>17020158</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -2388,10 +2422,10 @@
         <v>153</v>
       </c>
       <c r="C136">
-        <v>17021707</v>
+        <v>17053315</v>
       </c>
       <c r="D136">
-        <v>17021707</v>
+        <v>17053315</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
@@ -2399,10 +2433,10 @@
         <v>154</v>
       </c>
       <c r="C137">
-        <v>17021804</v>
+        <v>17021600</v>
       </c>
       <c r="D137">
-        <v>17021804</v>
+        <v>17021600</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -2410,10 +2444,10 @@
         <v>155</v>
       </c>
       <c r="C138">
-        <v>17106800</v>
+        <v>17017203</v>
       </c>
       <c r="D138">
-        <v>17106800</v>
+        <v>17017203</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -2421,10 +2455,10 @@
         <v>156</v>
       </c>
       <c r="C139">
-        <v>17050278</v>
+        <v>17021707</v>
       </c>
       <c r="D139">
-        <v>17050278</v>
+        <v>17021707</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -2432,10 +2466,10 @@
         <v>157</v>
       </c>
       <c r="C140">
-        <v>17043069</v>
+        <v>17021804</v>
       </c>
       <c r="D140">
-        <v>17043069</v>
+        <v>17021804</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -2443,10 +2477,10 @@
         <v>158</v>
       </c>
       <c r="C141">
-        <v>17018820</v>
+        <v>17106800</v>
       </c>
       <c r="D141">
-        <v>17018820</v>
+        <v>17106800</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
@@ -2454,10 +2488,10 @@
         <v>159</v>
       </c>
       <c r="C142">
-        <v>17043026</v>
+        <v>17050278</v>
       </c>
       <c r="D142">
-        <v>17043026</v>
+        <v>17050278</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
@@ -2465,10 +2499,10 @@
         <v>160</v>
       </c>
       <c r="C143">
-        <v>17039150</v>
+        <v>17043069</v>
       </c>
       <c r="D143">
-        <v>17039150</v>
+        <v>17043069</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
@@ -2476,10 +2510,10 @@
         <v>161</v>
       </c>
       <c r="C144">
-        <v>17052823</v>
+        <v>17018820</v>
       </c>
       <c r="D144">
-        <v>17052823</v>
+        <v>17018820</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
@@ -2487,10 +2521,10 @@
         <v>162</v>
       </c>
       <c r="C145">
-        <v>17051746</v>
+        <v>17043026</v>
       </c>
       <c r="D145">
-        <v>17051746</v>
+        <v>17043026</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -2498,10 +2532,10 @@
         <v>163</v>
       </c>
       <c r="C146">
-        <v>17049253</v>
+        <v>17039150</v>
       </c>
       <c r="D146">
-        <v>17049253</v>
+        <v>17039150</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -2509,14 +2543,50 @@
         <v>164</v>
       </c>
       <c r="C147">
+        <v>17052823</v>
+      </c>
+      <c r="D147">
+        <v>17052823</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C148">
+        <v>17051746</v>
+      </c>
+      <c r="D148">
+        <v>17051746</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C149">
+        <v>17049253</v>
+      </c>
+      <c r="D149">
+        <v>17049253</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C150">
         <v>17107806</v>
       </c>
-      <c r="D147">
+      <c r="D150">
         <v>17107806</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E22" r:id="rId1" xr:uid="{AEE0C3B0-1BF3-48EB-9EA3-5A746517858E}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>